--- a/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
+++ b/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-05" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,13 +38,13 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
+      <color rgb="00D03B3B"/>
+    </font>
+    <font>
       <color rgb="00898781"/>
     </font>
-    <font>
-      <color rgb="00D03B3B"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,10 +74,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,8 +97,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -536,49 +550,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>6963</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>2804500</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>72.83</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2986800</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 64.26偏近超买区，现价0.43高于50日均线0.334约29%，技术面信号偏强但需留意RSI压力。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,42 +610,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CEB</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1462000</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.23</v>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>56763300</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>1.46</v>
       </c>
       <c r="H3" t="n">
-        <v>68.88</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.272</v>
+        <v>76.48</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.236</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,42 +655,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0182</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1142100</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.12</v>
+          <t>CUSCAPI</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>17177200</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.74</v>
       </c>
       <c r="H4" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.307</v>
+        <v>30.46</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.073</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,42 +700,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NOTION</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.0213</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1043100</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.09</v>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>12081000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.28</v>
       </c>
       <c r="H5" t="n">
-        <v>67.48</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.591</v>
+        <v>71.78</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.215</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -723,42 +745,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-0.0165</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>963100</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.04</v>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0567</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>9559000</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.87</v>
       </c>
       <c r="H6" t="n">
-        <v>68.09</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.497</v>
+        <v>70.37</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.591</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,42 +790,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>860700</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.27</v>
+          <t>EFORCE</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>-0.3333</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>9293500</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
-        <v>62.66</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
+        <v>35.26</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.604</v>
+      <c r="J7" s="9" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.176</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -813,42 +835,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JFTECH</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>646900</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H8" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0.679</v>
-      </c>
+          <t>GBBOND</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>8357300</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -858,45 +873,3173 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>8224600</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H9" t="n">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>6897600</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H10" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1.763</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>1.589</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0178</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEDANIA</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>6297000</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H11" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>5657600</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H12" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>5548900</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H13" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>4806300</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H14" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>4753100</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GTA</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>3738400</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H16" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>3528500</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0131</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DFX</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>3315700</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H18" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.07969999999999999</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>3288100</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H19" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>3286800</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H20" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>3276200</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>3230800</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>3072900</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H23" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0470</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BFIELD</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>2701400</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.06559999999999999</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>2686900</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H25" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>2588000</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H26" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H27" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ENPRO</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>2260800</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H28" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>2212000</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H29" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>2196500</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H30" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>2047600</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1989600</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H32" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>5151</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>HEXTAR</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D33" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1852000</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K33" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H34" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>1712700</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>1653300</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H36" t="n">
+        <v>62.91</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VANTNRG</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1594600</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H37" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NEXG</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E38" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>646000</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F38" s="11" t="n">
+        <v>1552000</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H38" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1540100</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H39" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>1442400</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>4.883</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>4.597</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>1435200</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H41" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>1421300</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H42" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>1393900</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H43" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>2.502</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>1391600</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H44" t="n">
+        <v>69.87</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>3.836</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>3.348</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>1381400</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H45" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>1341200</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H46" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>1271300</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0398</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GDGROUP</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>1214500</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>-0.009899999999999999</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>1213200</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H49" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>-0.0696</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>1212800</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H50" t="n">
+        <v>40</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>2.327</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>1206600</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>1184600</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H52" t="n">
+        <v>75.23</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>1150200</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H53" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>2.569</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>2.552</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>1146900</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H54" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>1146600</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H55" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>1106200</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H56" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>2.103</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>1090300</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>1055200</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H58" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>1037900</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H59" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>3.605</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>1013500</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H60" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EXSIMHB</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>994700</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H61" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>969500</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H62" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>951600</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H63" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>943500</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H64" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>4.786</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>4.924</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>918200</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H65" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>2.849</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>2.741</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>904000</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>2.556</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>902500</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H67" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>893100</v>
+      </c>
+      <c r="G68" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="H9" t="n">
-        <v>50.57</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>870400</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>861700</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H70" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>5.587</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>5.734</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>780300</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H71" t="n">
+        <v>72.98</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>6.871</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>732900</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H72" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>636600</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H73" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>626500</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>73.06999999999999</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>622900</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H75" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>604500</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H76" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>574000</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>2.057</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>555300</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H78" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>547200</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H79" t="n">
+        <v>73.03</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>2.306</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
+++ b/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-05" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -89,15 +89,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.43</v>
+        <v>0.445</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0238</v>
+        <v>0.0595</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2986800</v>
+        <v>7664100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.26000000000001</v>
+        <v>66.95</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.392</v>
+        <v>0.394</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.334</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 64.26偏近超买区，现价0.43高于50日均线0.334约29%，技术面信号偏强但需留意RSI压力。</t>
+          <t>现价0.445高于50日均线0.334，SAR转多信号获均线支撑；RSI 66.95接近超买区，动能偏强但上行空间受限。</t>
         </is>
       </c>
     </row>
@@ -610,39 +610,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.32</v>
+        <v>0.075</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.1034</v>
+        <v>-0.3478</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>56763300</v>
+        <v>69175300</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1.46</v>
+        <v>0.14</v>
       </c>
       <c r="H3" t="n">
-        <v>76.48</v>
+        <v>15.25</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.252</v>
+        <v>0.219</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>0.236</v>
+        <v>0.436</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="14" t="inlineStr"/>
@@ -655,39 +655,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.045</v>
+        <v>0.315</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.1</v>
+        <v>0.0862</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>17177200</v>
+        <v>68690200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.74</v>
+        <v>1.77</v>
       </c>
       <c r="H4" t="n">
-        <v>30.46</v>
+        <v>75.66</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.055</v>
+        <v>0.251</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.073</v>
+        <v>0.236</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,39 +700,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.385</v>
+        <v>0.04</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.0405</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>12081000</v>
+        <v>34432000</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.28</v>
+        <v>1.48</v>
       </c>
       <c r="H5" t="n">
-        <v>71.78</v>
+        <v>26.88</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.344</v>
+        <v>0.055</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.215</v>
+        <v>0.073</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>20377800</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H6" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
         <v>0.745</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>0.0567</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>9559000</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H6" t="n">
-        <v>70.37</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.652</v>
-      </c>
       <c r="K6" s="9" t="n">
-        <v>0.591</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -801,19 +801,19 @@
       <c r="D7" s="9" t="n">
         <v>0.14</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="10" t="n">
         <v>-0.3333</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9293500</v>
+        <v>18554300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.67</v>
+        <v>3.34</v>
       </c>
       <c r="H7" t="n">
         <v>35.26</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -835,33 +835,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.1111</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>8357300</v>
+        <v>16003700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.17</v>
+        <v>3.95</v>
+      </c>
+      <c r="H8" t="n">
+        <v>83.04000000000001</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.089</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -873,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0097</v>
+        <v>0.385</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.0405</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8224600</v>
+        <v>12116000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H9" t="n">
-        <v>66.54000000000001</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
+        <v>71.78</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.48</v>
+        <v>0.344</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.475</v>
+        <v>0.215</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -918,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0164</v>
+        <v>0.73</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.0355</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>6897600</v>
+        <v>11910200</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.31</v>
+        <v>1.08</v>
       </c>
       <c r="H10" t="n">
-        <v>62.48</v>
+        <v>68.7</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.763</v>
+        <v>0.651</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1.589</v>
+        <v>0.591</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -963,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.1053</v>
+        <v>0.18</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6297000</v>
+        <v>11154400</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.92</v>
+        <v>0.18</v>
       </c>
       <c r="H11" t="n">
-        <v>56.09</v>
+        <v>64.31</v>
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.1</v>
+        <v>0.162</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.098</v>
+        <v>0.126</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1008,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.0545</v>
+        <v>-0.0083</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>5657600</v>
+        <v>10551000</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.57</v>
+        <v>0.41</v>
       </c>
       <c r="H12" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
+        <v>70.97</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.27</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.307</v>
+        <v>0.498</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1053,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.785</v>
+        <v>0.51</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0329</v>
+        <v>-0.0097</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5548900</v>
+        <v>10207000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="H13" t="n">
-        <v>61.97</v>
+        <v>62.93</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.743</v>
+        <v>0.479</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.475</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1098,40 +1105,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.235</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4806300</v>
+        <v>9213800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H14" t="n">
-        <v>68.23</v>
+        <v>0.19</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>0.632</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1143,39 +1143,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>0</v>
+        <v>1.85</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4753100</v>
+        <v>9195000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H15" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
+        <v>61.82</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.406</v>
+        <v>1.762</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.411</v>
+        <v>1.588</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1188,36 +1188,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0043</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MTRONIC</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.0185</v>
+        <v>0.005</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3738400</v>
+        <v>8050000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.23</v>
+        <v>14.78</v>
       </c>
       <c r="H16" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
+        <v>46.51</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="J16" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.006</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1229,39 +1233,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.655</v>
+        <v>0.29</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.0076</v>
+        <v>0.0545</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>3528500</v>
+        <v>7489500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.19</v>
+        <v>0.75</v>
       </c>
       <c r="H17" t="n">
-        <v>70.73999999999999</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
+        <v>56.14</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.5</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1274,39 +1278,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0548</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>3315700</v>
+        <v>7337200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.82</v>
+        <v>1.13</v>
       </c>
       <c r="H18" t="n">
-        <v>79.41</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.1</v>
+        <v>0.706</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.089</v>
+        <v>0.632</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1319,39 +1323,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.105</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.1053</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>3288100</v>
+        <v>7062700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>3.29</v>
+        <v>2.15</v>
       </c>
       <c r="H19" t="n">
-        <v>64.01000000000001</v>
+        <v>56.09</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.68</v>
+        <v>0.1</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.679</v>
+        <v>0.098</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1364,39 +1368,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3286800</v>
+        <v>6843500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="H20" t="n">
-        <v>68.88</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
+        <v>69.54000000000001</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.284</v>
+        <v>0.556</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.272</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1409,39 +1413,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>0.04</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>3276200</v>
+        <v>6086100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.13</v>
+        <v>0.62</v>
       </c>
       <c r="H21" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
+        <v>58.2</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.569</v>
+        <v>0.035</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.498</v>
+        <v>0.033</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1454,36 +1458,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0.0189</v>
+        <v>0.3</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3230800</v>
+        <v>5463100</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.25</v>
+        <v>0.87</v>
       </c>
       <c r="H22" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+        <v>68.88</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.272</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1495,39 +1503,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.19</v>
+        <v>0.395</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.027</v>
+        <v>-0.0125</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3072900</v>
+        <v>4976600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="H23" t="n">
-        <v>48.79</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
+        <v>38.38</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.194</v>
+        <v>0.406</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.181</v>
+        <v>0.411</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1540,33 +1548,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2701400</v>
+        <v>4471500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+        <v>0.29</v>
+      </c>
+      <c r="H24" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.424</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1578,40 +1593,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.48</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>2686900</v>
+        <v>4277400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H25" t="n">
-        <v>78.01000000000001</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>0.789</v>
-      </c>
+        <v>0.29</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1623,39 +1631,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0</v>
+        <v>1.09</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0481</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>2588000</v>
+        <v>4144100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H26" t="n">
-        <v>62.52</v>
+        <v>54.54</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.338</v>
+        <v>1.069</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.319</v>
+        <v>1.029</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1668,39 +1676,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2350000</v>
+        <v>4063800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="H27" t="n">
         <v>66.31</v>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.507</v>
+        <v>0.38</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.424</v>
+        <v>0.373</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1713,39 +1721,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0367</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2260800</v>
+        <v>3987300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>57.33</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
+        <v>76.83</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.266</v>
+        <v>1.041</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.227</v>
+        <v>0.884</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1758,40 +1766,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0.0163</v>
+        <v>0.275</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2212000</v>
+        <v>3843100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.72</v>
+        <v>0.24</v>
       </c>
       <c r="H29" t="n">
-        <v>62.98</v>
+        <v>18.18</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>0.577</v>
-      </c>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
     </row>
@@ -1803,39 +1807,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.36</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2196500</v>
+        <v>3683100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="H30" t="n">
-        <v>66.31</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
+        <v>64.34</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.38</v>
+        <v>0.339</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.373</v>
+        <v>0.319</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1848,40 +1852,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0265</v>
+        <v>0.265</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2047600</v>
+        <v>3547600</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H31" t="n">
-        <v>53.48</v>
+        <v>25.81</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>0.771</v>
-      </c>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
     </row>
@@ -1893,39 +1893,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.235</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1989600</v>
+        <v>3500100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="H32" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
+        <v>30.7</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.607</v>
+        <v>0.261</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.608</v>
+        <v>0.314</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1938,39 +1938,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.74</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.0725</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1852000</v>
+        <v>3493100</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.13</v>
+        <v>3.5</v>
       </c>
       <c r="H33" t="n">
-        <v>53.15</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
+        <v>63.3</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.774</v>
+        <v>0.68</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.775</v>
+        <v>0.679</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1983,39 +1983,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0.0214</v>
+        <v>0.78</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1729000</v>
+        <v>3412100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H34" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
+        <v>53.15</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.774</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.67</v>
+        <v>0.775</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2028,39 +2028,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.445</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.023</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1712700</v>
+        <v>3181300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="H35" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
+        <v>60.74</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.322</v>
+        <v>0.411</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.338</v>
+        <v>0.407</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.385</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>-0.0175</v>
+        <v>0.0267</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1653300</v>
+        <v>3138300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H36" t="n">
-        <v>62.91</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
+        <v>75.23</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.525</v>
+        <v>0.342</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.479</v>
+        <v>0.316</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2118,39 +2118,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>-0.0149</v>
+        <v>0.027</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1594600</v>
+        <v>3104600</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.41</v>
+        <v>0.13</v>
       </c>
       <c r="H37" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
+        <v>48.79</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.337</v>
+        <v>0.194</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.334</v>
+        <v>0.181</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2163,39 +2163,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1552000</v>
+        <v>2967100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.09</v>
+        <v>0.42</v>
       </c>
       <c r="H38" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.29</v>
+        <v>1.016</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.278</v>
+        <v>0.788</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2208,39 +2208,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1.13</v>
+        <v>0.275</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.0367</v>
+        <v>-0.0179</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1540100</v>
+        <v>2841400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="H39" t="n">
-        <v>76.83</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
+        <v>55.67</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>1.041</v>
+        <v>0.265</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.884</v>
+        <v>0.227</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2253,39 +2253,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>5.09</v>
+        <v>0.62</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>-0.002</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1442400</v>
+        <v>2788200</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.06</v>
+        <v>0.91</v>
       </c>
       <c r="H40" t="n">
-        <v>68.28</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
+        <v>62.03</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>4.883</v>
+        <v>0.579</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>4.597</v>
+        <v>0.577</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2298,39 +2298,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.435</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E41" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1435200</v>
+        <v>2765900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H41" t="n">
-        <v>58.54</v>
+        <v>50.21</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.407</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2343,39 +2343,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.63</v>
+        <v>5.05</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.0328</v>
+        <v>-0.0098</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1421300</v>
+        <v>2764700</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.65</v>
+        <v>0.11</v>
       </c>
       <c r="H42" t="n">
-        <v>70.86</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
+        <v>65.03</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.528</v>
+        <v>4.879</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.432</v>
+        <v>4.597</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2388,39 +2388,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.081</v>
+        <v>0.78</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1393900</v>
+        <v>2762600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H43" t="n">
-        <v>75.56</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
+        <v>55.82</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.502</v>
+        <v>0.769</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.918</v>
+        <v>0.771</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2442,30 +2442,30 @@
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0216</v>
+        <v>4.22</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.012</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1391600</v>
+        <v>2699600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="H44" t="n">
-        <v>69.87</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
+        <v>69.03</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>3.836</v>
+        <v>3.832</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>3.348</v>
+        <v>3.347</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2478,39 +2478,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0.0259</v>
+        <v>0.715</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1381400</v>
+        <v>2632800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.91</v>
+        <v>0.39</v>
       </c>
       <c r="H45" t="n">
-        <v>63.67</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
+        <v>56.65</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.109</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.074</v>
+        <v>0.67</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2523,39 +2523,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.0155</v>
+        <v>0.575</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1341200</v>
+        <v>2592800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.33</v>
+        <v>0.58</v>
       </c>
       <c r="H46" t="n">
-        <v>57.8</v>
+        <v>67.37</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.255</v>
+        <v>0.526</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.167</v>
+        <v>0.48</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2568,33 +2568,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.61</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1271300</v>
+        <v>2304300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
+        <v>0.22</v>
+      </c>
+      <c r="H47" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.608</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
     </row>
@@ -2606,39 +2613,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0132</v>
+        <v>3.03</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0669</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1214500</v>
+        <v>2251300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1.3</v>
+        <v>0.67</v>
       </c>
       <c r="H48" t="n">
-        <v>58.64</v>
+        <v>74.89</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.378</v>
+        <v>2.499</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.38</v>
+        <v>1.917</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2651,39 +2658,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>-0.009899999999999999</v>
+        <v>2.1</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1213200</v>
+        <v>2245500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.03</v>
+        <v>3.13</v>
       </c>
       <c r="H49" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
+        <v>38.01</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.585</v>
+        <v>2.267</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.792</v>
+        <v>2.326</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2696,39 +2703,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>-0.0696</v>
+        <v>0.515</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1212800</v>
+        <v>2040200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.69</v>
+        <v>0.33</v>
       </c>
       <c r="H50" t="n">
-        <v>40</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
+        <v>47.66</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.271</v>
+        <v>0.52</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.327</v>
+        <v>0.532</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2741,39 +2748,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1206600</v>
+        <v>2007000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>1.05</v>
+        <v>0.35</v>
       </c>
       <c r="H51" t="n">
-        <v>41.88</v>
+        <v>56.19</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.426</v>
+        <v>0.322</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.445</v>
+        <v>0.338</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2786,39 +2793,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.0267</v>
+        <v>0.3</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1184600</v>
+        <v>1974000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="H52" t="n">
-        <v>75.23</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
+        <v>54.88</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.342</v>
+        <v>0.29</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.316</v>
+        <v>0.278</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2831,39 +2838,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0156</v>
+        <v>2.59</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1150200</v>
+        <v>1931500</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="H53" t="n">
-        <v>55.63</v>
+        <v>53.21</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.569</v>
+        <v>2.57</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.552</v>
+        <v>2.469</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2876,39 +2883,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0234</v>
+        <v>0.795</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0258</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1146900</v>
+        <v>1905500</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.31</v>
+        <v>0.74</v>
       </c>
       <c r="H54" t="n">
-        <v>59.74</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
+        <v>58.73</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.629</v>
+        <v>0.764</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.593</v>
+        <v>0.743</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2921,39 +2928,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0323</v>
+        <v>1.19</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0348</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1146600</v>
+        <v>1897900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="H55" t="n">
-        <v>59.66</v>
+        <v>56.49</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.764</v>
+        <v>1.157</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.743</v>
+        <v>1.111</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2966,39 +2973,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.05</v>
+        <v>0.805</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>-0.0049</v>
+        <v>0.0126</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1106200</v>
+        <v>1882600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H56" t="n">
-        <v>42.11</v>
+        <v>62.76</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.103</v>
+        <v>0.746</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.073</v>
+        <v>0.7</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3011,39 +3018,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1090300</v>
+        <v>1874500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H57" t="n">
-        <v>48.15</v>
+        <v>68.36</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.065</v>
+        <v>0.775</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.028</v>
+        <v>0.759</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3056,39 +3063,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.515</v>
+        <v>0.22</v>
       </c>
       <c r="E58" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1055200</v>
+        <v>1857700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="H58" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
+        <v>40.5</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.532</v>
+        <v>0.245</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3101,39 +3108,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>-0.011</v>
+        <v>2.06</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1037900</v>
+        <v>1834300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H59" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
+        <v>43.41</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>3.605</v>
+        <v>2.104</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.583</v>
+        <v>2.073</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3146,39 +3153,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0.0252</v>
+        <v>0.265</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1013500</v>
+        <v>1758300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
       </c>
       <c r="H60" t="n">
-        <v>63.96</v>
+        <v>66.58</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.747</v>
+        <v>0.239</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.7</v>
+        <v>0.214</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3191,40 +3198,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EXSIMHB</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0.01</v>
+        <v>0.315</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>994700</v>
+        <v>1726800</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H61" t="n">
-        <v>62.2</v>
+        <v>0.15</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="K61" s="9" t="n">
-        <v>0.471</v>
-      </c>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
     </row>
@@ -3236,39 +3236,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0</v>
+        <v>0.505</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.1855</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>969500</v>
+        <v>1726400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.18</v>
+        <v>1.7</v>
       </c>
       <c r="H62" t="n">
-        <v>57.03</v>
+        <v>8.35</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.896</v>
+        <v>0.617</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.856</v>
+        <v>0.633</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3281,39 +3281,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.23</v>
+        <v>0.33</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.0424</v>
+        <v>-0.0149</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>951600</v>
+        <v>1723600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H63" t="n">
-        <v>67.75</v>
+        <v>44.39</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.112</v>
+        <v>0.337</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.123</v>
+        <v>0.334</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3326,39 +3326,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.655</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0738</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>943500</v>
+        <v>1720700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.06</v>
+        <v>0.78</v>
       </c>
       <c r="H64" t="n">
-        <v>38.61</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>4.786</v>
+        <v>0.53</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>4.924</v>
+        <v>0.433</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3371,39 +3371,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>3.1</v>
+        <v>3.53</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.0131</v>
+        <v>-0.0302</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>918200</v>
+        <v>1656000</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="H65" t="n">
-        <v>65.61</v>
+        <v>53.09</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.849</v>
+        <v>3.598</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.741</v>
+        <v>2.581</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3416,39 +3416,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.87</v>
+        <v>0.5</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.0141</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>904000</v>
+        <v>1612000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H66" t="n">
-        <v>59.89</v>
+        <v>26.49</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.73</v>
+        <v>0.585</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.556</v>
+        <v>0.792</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3461,39 +3461,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>902500</v>
+        <v>1603900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.28</v>
+        <v>1.06</v>
       </c>
       <c r="H67" t="n">
-        <v>62.66</v>
+        <v>62.61</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.636</v>
+        <v>1.108</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.604</v>
+        <v>1.074</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3506,39 +3506,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.65</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>893100</v>
+        <v>1577500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.05</v>
+        <v>0.43</v>
       </c>
       <c r="H68" t="n">
-        <v>53.21</v>
+        <v>58.62</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.57</v>
+        <v>0.628</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.469</v>
+        <v>0.593</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3551,39 +3551,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>870400</v>
+        <v>1570500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.06</v>
+        <v>0.58</v>
       </c>
       <c r="H69" t="n">
-        <v>50.21</v>
+        <v>66.83</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.111</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.123</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3596,39 +3596,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0173</v>
+        <v>1.32</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>861700</v>
+        <v>1529900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="H70" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
+        <v>58.61</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>5.587</v>
+        <v>1.256</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>5.734</v>
+        <v>1.168</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3641,39 +3641,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.033</v>
+        <v>2.83</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>780300</v>
+        <v>1507100</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H71" t="n">
-        <v>72.98</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
+        <v>58.2</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>6.871</v>
+        <v>2.726</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>6.62</v>
+        <v>2.555</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3686,39 +3686,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.03</v>
+        <v>2.62</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>732900</v>
+        <v>1451200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.09</v>
+        <v>0.27</v>
       </c>
       <c r="H72" t="n">
-        <v>65.7</v>
+        <v>56.67</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.951</v>
+        <v>2.57</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.796</v>
+        <v>2.553</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3731,39 +3731,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>2.83</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>636600</v>
+        <v>1374400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H73" t="n">
-        <v>61.79</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.481</v>
+        <v>2.49</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.474</v>
+        <v>2.055</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3776,39 +3776,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0252</v>
+        <v>4.7</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>626500</v>
+        <v>1330100</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H74" t="n">
-        <v>73.06999999999999</v>
+        <v>35.6</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.777</v>
+        <v>4.784</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.759</v>
+        <v>4.923</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.5</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>622900</v>
+        <v>1327300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="H75" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
+        <v>26.55</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.151</v>
+        <v>0.54</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.157</v>
+        <v>0.579</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3866,39 +3866,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.635</v>
+        <v>2.21</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0.0242</v>
+        <v>-0.0134</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>604500</v>
+        <v>1297300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="H76" t="n">
-        <v>56.62</v>
+        <v>45.31</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.61</v>
+        <v>2.269</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.608</v>
+        <v>2.213</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3911,39 +3911,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.0247</v>
+        <v>0.385</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>574000</v>
+        <v>1259500</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.2</v>
+        <v>1.35</v>
       </c>
       <c r="H77" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
+        <v>58.64</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.497</v>
+        <v>0.378</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.057</v>
+        <v>0.38</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3956,39 +3956,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.0254</v>
+        <v>0.42</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>555300</v>
+        <v>1253400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.14</v>
+        <v>1.09</v>
       </c>
       <c r="H78" t="n">
-        <v>66.83</v>
+        <v>41.88</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.137</v>
+        <v>0.426</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.043</v>
+        <v>0.445</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4001,45 +4001,1395 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.0488</v>
+        <v>7.87</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0396</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>547200</v>
+        <v>1244300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="H79" t="n">
-        <v>73.03</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
+        <v>73.53</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.306</v>
+        <v>6.876</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.084</v>
+        <v>6.621</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H80" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>1182800</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H81" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>2.847</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>2.741</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EXSIMHB</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>1138400</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H82" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>1133300</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H83" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>5.587</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>5.734</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>1101700</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H84" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H85" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>971100</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H86" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>9.808</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>9.295</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>964200</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H87" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>913500</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H88" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>883700</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H89" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>873400</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>10.109</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>10.261</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>827100</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H91" t="n">
+        <v>73.03</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>2.306</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>816300</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H92" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>801000</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H93" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>791900</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H94" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>782600</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H95" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>725000</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H96" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>685000</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H97" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>652600</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H98" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>650300</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H99" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>1.926</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>637300</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H100" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>582400</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H101" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>578100</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H102" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.0165</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>566600</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H103" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>559400</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H104" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>549700</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H105" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>5.228</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>5.286</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>535200</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H106" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>523400</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H107" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>3.222</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>3.426</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>518000</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H108" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>WCEHB</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>506700</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H109" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M79"/>
+  <autoFilter ref="A1:M109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
+++ b/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-05" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.445</v>
+        <v>0.435</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.0357</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>7664100</v>
+        <v>8828600</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.95</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.334</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.445高于50日均线0.334，SAR转多信号获均线支撑；RSI 66.95接近超买区，动能偏强但上行空间受限。</t>
+          <t>SAR转多，现价0.435高于50日均线0.334约30%，RSI 65.21接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-0.3478</v>
+        <v>-0.3913</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>69175300</v>
+        <v>560004700</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.14</v>
+        <v>1.14</v>
       </c>
       <c r="H3" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.219</v>
+        <v>0.218</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.436</v>
@@ -670,10 +670,10 @@
         <v>0.0862</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>68690200</v>
+        <v>86667100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="H4" t="n">
         <v>75.66</v>
@@ -715,10 +715,10 @@
         <v>-0.2</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>34432000</v>
+        <v>40469500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="H5" t="n">
         <v>26.88</v>
@@ -745,28 +745,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.0592</v>
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>-0.2857</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>20377800</v>
+        <v>31241600</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.44</v>
+        <v>5.62</v>
       </c>
       <c r="H6" t="n">
-        <v>64.98999999999999</v>
+        <v>37.22</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.745</v>
+        <v>0.197</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-0.3333</v>
+        <v>0.795</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0461</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>18554300</v>
+        <v>23194200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>3.34</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>35.26</v>
+        <v>63.54</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.196</v>
+        <v>0.744</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.176</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.1111</v>
+        <v>0.0741</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>16003700</v>
+        <v>17682800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>3.95</v>
+        <v>4.36</v>
       </c>
       <c r="H8" t="n">
-        <v>83.04000000000001</v>
+        <v>81.98</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
@@ -880,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.0405</v>
+        <v>0.51</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12116000</v>
+        <v>15033900</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>71.78</v>
+        <v>62.93</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.344</v>
+        <v>0.479</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.215</v>
+        <v>0.475</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.73</v>
+        <v>1.86</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.0355</v>
+        <v>0.0164</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>11910200</v>
+        <v>13895700</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
       <c r="H10" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.48</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.651</v>
+        <v>1.763</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.591</v>
+        <v>1.589</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +970,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11154400</v>
+        <v>13861000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
       <c r="H11" t="n">
-        <v>64.31</v>
+        <v>70.97</v>
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.162</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.126</v>
+        <v>0.498</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0083</v>
+        <v>0.725</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0284</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>10551000</v>
+        <v>13747200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.41</v>
+        <v>1.25</v>
       </c>
       <c r="H12" t="n">
-        <v>70.97</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.498</v>
+        <v>0.591</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.51</v>
+        <v>0.635</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>-0.0097</v>
+        <v>-0.0379</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>10207000</v>
+        <v>12417400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="H13" t="n">
-        <v>62.93</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.479</v>
+        <v>0.555</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.475</v>
+        <v>0.5</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,33 +1105,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.235</v>
+        <v>0.38</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.0217</v>
+        <v>0.027</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9213800</v>
+        <v>12257100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+        <v>0.29</v>
+      </c>
+      <c r="H14" t="n">
+        <v>70.89</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.215</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
     </row>
@@ -1143,39 +1150,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.18</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>9195000</v>
+        <v>12014800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
       <c r="H15" t="n">
-        <v>61.82</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.31</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.762</v>
+        <v>0.162</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.588</v>
+        <v>0.126</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1188,40 +1195,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0043</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MTRONIC</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8050000</v>
+        <v>11775800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="H16" t="n">
-        <v>46.51</v>
+        <v>0.24</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J16" s="9" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.29</v>
+        <v>0.295</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.0545</v>
+        <v>0.0727</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7489500</v>
+        <v>9845900</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="H17" t="n">
-        <v>56.14</v>
+        <v>57.83</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0.307</v>
@@ -1278,28 +1278,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0548</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7337200</v>
+        <v>8656600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>67.01000000000001</v>
+        <v>66.31</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.706</v>
+        <v>0.507</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.632</v>
+        <v>0.424</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,28 +1323,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0043</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>MTRONIC</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.1053</v>
+        <v>0.005</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7062700</v>
+        <v>8140000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.15</v>
+        <v>14.95</v>
       </c>
       <c r="H19" t="n">
-        <v>56.09</v>
+        <v>46.51</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.1</v>
+        <v>0.006</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.098</v>
+        <v>0.006</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1368,28 +1368,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>-0.0152</v>
+        <v>0.785</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.07530000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6843500</v>
+        <v>8054100</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.36</v>
+        <v>1.25</v>
       </c>
       <c r="H20" t="n">
-        <v>69.54000000000001</v>
+        <v>68.81</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.556</v>
+        <v>0.707</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.5</v>
+        <v>0.632</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,39 +1413,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.1111</v>
+        <v>0.105</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.1053</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6086100</v>
+        <v>7252500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.62</v>
+        <v>2.21</v>
       </c>
       <c r="H21" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.09</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.035</v>
+        <v>0.1</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.033</v>
+        <v>0.098</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1458,40 +1458,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.3</v>
+        <v>0.005</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5463100</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H22" t="n">
-        <v>68.88</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.272</v>
-      </c>
+        <v>7087300</v>
+      </c>
+      <c r="G22" s="12" t="n"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1503,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.0125</v>
+        <v>0.3</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4976600</v>
+        <v>6550900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.44</v>
+        <v>1.05</v>
       </c>
       <c r="H23" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.88</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.406</v>
+        <v>0.284</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.411</v>
+        <v>0.272</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1548,28 +1539,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0.0177</v>
+        <v>0.04</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.1111</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4471500</v>
+        <v>6123600</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="H24" t="n">
-        <v>67.59999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1577,10 +1568,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.508</v>
+        <v>0.035</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.424</v>
+        <v>0.033</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1593,33 +1584,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0</v>
+        <v>5.03</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4277400</v>
+        <v>5812200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>63.51</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
+      <c r="J25" s="9" t="n">
+        <v>4.878</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>4.596</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1631,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0481</v>
+        <v>0.39</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4144100</v>
+        <v>5555800</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="H26" t="n">
-        <v>54.54</v>
+        <v>35.03</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1660,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.069</v>
+        <v>0.405</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.029</v>
+        <v>0.411</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1676,28 +1674,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.0127</v>
+        <v>0.0303</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4063800</v>
+        <v>5267500</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="H27" t="n">
-        <v>66.31</v>
+        <v>56.66</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1705,10 +1703,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.373</v>
+        <v>0.147</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1721,40 +1719,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1.13</v>
+        <v>0.27</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.0367</v>
+        <v>0.0189</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3987300</v>
+        <v>5109400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H28" t="n">
-        <v>76.83</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>1.041</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>0.884</v>
-      </c>
+        <v>27.8</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1766,36 +1760,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.275</v>
+        <v>0.36</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.0141</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3843100</v>
+        <v>4908800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.24</v>
+        <v>0.66</v>
       </c>
       <c r="H29" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
+        <v>64.34</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.319</v>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
     </row>
@@ -1807,28 +1805,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0141</v>
+        <v>0.0127</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3683100</v>
+        <v>4888400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="H30" t="n">
-        <v>64.34</v>
+        <v>66.31</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
@@ -1836,10 +1834,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.339</v>
+        <v>0.38</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.319</v>
+        <v>0.373</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1852,36 +1850,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0367</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3547600</v>
+        <v>4885200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="H31" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
+        <v>76.83</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.884</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
     </row>
@@ -1893,39 +1895,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.235</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3500100</v>
+        <v>4820400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="H32" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.261</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.314</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1938,39 +1940,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0.0725</v>
+        <v>0.0385</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3493100</v>
+        <v>4720800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3.5</v>
+        <v>0.41</v>
       </c>
       <c r="H33" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.09</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.68</v>
+        <v>1.068</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.679</v>
+        <v>1.028</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1998,10 +2000,10 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3412100</v>
+        <v>4595000</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="H34" t="n">
         <v>53.15</v>
@@ -2028,40 +2030,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.023</v>
+        <v>0.48</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3181300</v>
+        <v>4522600</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H35" t="n">
-        <v>60.74</v>
+        <v>0.31</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J35" s="9" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>0.407</v>
-      </c>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
     </row>
@@ -2073,28 +2068,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.385</v>
+        <v>0.745</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>0.0267</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3138300</v>
+        <v>4145200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.38</v>
+        <v>4.15</v>
       </c>
       <c r="H36" t="n">
-        <v>75.23</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2102,10 +2097,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.342</v>
+        <v>0.68</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.316</v>
+        <v>0.679</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2118,39 +2113,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.19</v>
+        <v>0.445</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3104600</v>
+        <v>4134600</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="H37" t="n">
-        <v>48.79</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.74</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.194</v>
+        <v>0.411</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.181</v>
+        <v>0.407</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2163,28 +2158,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1.26</v>
+        <v>0.38</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.0328</v>
+        <v>0.0133</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2967100</v>
+        <v>4036700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="H38" t="n">
-        <v>76.56999999999999</v>
+        <v>74</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2192,10 +2187,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.016</v>
+        <v>0.342</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.788</v>
+        <v>0.315</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2208,28 +2203,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0179</v>
+        <v>2.6</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2841400</v>
+        <v>3998200</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="H39" t="n">
-        <v>55.67</v>
+        <v>53.96</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2237,10 +2232,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.265</v>
+        <v>2.571</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.227</v>
+        <v>2.469</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2253,40 +2248,36 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.62</v>
+        <v>0.275</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0185</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2788200</v>
+        <v>3900400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.91</v>
+        <v>0.24</v>
       </c>
       <c r="H40" t="n">
-        <v>62.03</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>0.577</v>
-      </c>
+        <v>18.18</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
     </row>
@@ -2298,39 +2289,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2765900</v>
+        <v>3818700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H41" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>29.3</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.261</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.314</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2343,28 +2334,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.0098</v>
+        <v>1.28</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.08470000000000001</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2764700</v>
+        <v>3619300</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.11</v>
+        <v>1.35</v>
       </c>
       <c r="H42" t="n">
-        <v>65.03</v>
+        <v>71.66</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2372,10 +2363,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.879</v>
+        <v>1.116</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.597</v>
+        <v>1.124</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2388,39 +2379,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.78</v>
+        <v>1.27</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>0.0331</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2762600</v>
+        <v>3445200</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="H43" t="n">
-        <v>55.82</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.95</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.769</v>
+        <v>1.017</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.771</v>
+        <v>0.788</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2433,39 +2424,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.012</v>
+        <v>0.32</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2699600</v>
+        <v>3367800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="H44" t="n">
-        <v>69.03</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.57</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>3.832</v>
+        <v>0.336</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>3.347</v>
+        <v>0.334</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2478,39 +2469,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.0214</v>
+        <v>0.155</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2632800</v>
+        <v>3307900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="H45" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.23</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.172</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.67</v>
+        <v>0.208</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2523,28 +2514,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.575</v>
+        <v>0.705</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2592800</v>
+        <v>3307700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="H46" t="n">
-        <v>67.37</v>
+        <v>54.98</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2552,10 +2543,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.526</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2568,39 +2559,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.61</v>
+        <v>0.785</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.0397</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2304300</v>
+        <v>3269000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="H47" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.93</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.607</v>
+        <v>0.77</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.608</v>
+        <v>0.771</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2613,39 +2604,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>3.03</v>
+        <v>0.195</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>0.0669</v>
+        <v>0.1143</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2251300</v>
+        <v>3236200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H48" t="n">
-        <v>74.89</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.47</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.499</v>
+        <v>0.165</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.917</v>
+        <v>0.165</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2658,39 +2649,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.66</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.08199999999999999</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2245500</v>
+        <v>3211400</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>3.13</v>
+        <v>1.46</v>
       </c>
       <c r="H49" t="n">
-        <v>38.01</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.40000000000001</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.267</v>
+        <v>0.531</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.326</v>
+        <v>0.433</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2703,39 +2694,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0</v>
+        <v>4.25</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2040200</v>
+        <v>3153100</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="H50" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.67</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.52</v>
+        <v>3.835</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.532</v>
+        <v>3.348</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2748,39 +2739,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.335</v>
+        <v>0.19</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>0.0152</v>
+        <v>0.027</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2007000</v>
+        <v>3114700</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="H51" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.79</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.322</v>
+        <v>0.194</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.338</v>
+        <v>0.181</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2793,39 +2784,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.0348</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1974000</v>
+        <v>3102900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H52" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.49</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.29</v>
+        <v>1.157</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.278</v>
+        <v>1.111</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2838,39 +2829,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.615</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1931500</v>
+        <v>3046400</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.11</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>53.21</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.02</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.57</v>
+        <v>0.579</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.469</v>
+        <v>0.577</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2883,28 +2874,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.795</v>
+        <v>0.335</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.0258</v>
+        <v>0.0152</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1905500</v>
+        <v>3017500</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H54" t="n">
-        <v>58.73</v>
+        <v>56.19</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2912,10 +2903,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.764</v>
+        <v>0.322</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.743</v>
+        <v>0.338</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2928,28 +2919,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0348</v>
+        <v>2.21</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0134</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1897900</v>
+        <v>2997400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H55" t="n">
-        <v>56.49</v>
+        <v>45.31</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2957,10 +2948,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.157</v>
+        <v>2.269</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.111</v>
+        <v>2.213</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2973,39 +2964,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0126</v>
+        <v>2.05</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1882600</v>
+        <v>2889000</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H56" t="n">
-        <v>62.76</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.11</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.746</v>
+        <v>2.103</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.7</v>
+        <v>2.073</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3018,39 +3009,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.0063</v>
+        <v>0.275</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1874500</v>
+        <v>2841400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="H57" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.67</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.775</v>
+        <v>0.265</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.759</v>
+        <v>0.227</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3063,39 +3054,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1857700</v>
+        <v>2829800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.09</v>
+        <v>0.63</v>
       </c>
       <c r="H58" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.37</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.23</v>
+        <v>0.526</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.245</v>
+        <v>0.48</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3108,39 +3099,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1834300</v>
+        <v>2820900</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="H59" t="n">
-        <v>43.41</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.33</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.104</v>
+        <v>0.607</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.073</v>
+        <v>0.608</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3153,28 +3144,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0192</v>
+        <v>2.15</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1758300</v>
+        <v>2636300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.51</v>
+        <v>3.67</v>
       </c>
       <c r="H60" t="n">
-        <v>66.58</v>
+        <v>40.53</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3182,10 +3173,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.239</v>
+        <v>2.272</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.214</v>
+        <v>2.327</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3198,33 +3189,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.315</v>
+        <v>3.02</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.0328</v>
+        <v>0.0634</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1726800</v>
+        <v>2607300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
+        <v>0.78</v>
+      </c>
+      <c r="H61" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>2.498</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>1.917</v>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
     </row>
@@ -3236,28 +3234,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.505</v>
+        <v>0.51</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>-0.1855</v>
+        <v>-0.0097</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1726400</v>
+        <v>2533300</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.7</v>
+        <v>0.41</v>
       </c>
       <c r="H62" t="n">
-        <v>8.35</v>
+        <v>46</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3265,10 +3263,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.617</v>
+        <v>0.52</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.633</v>
+        <v>0.531</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3281,28 +3279,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0149</v>
+        <v>0.305</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1723600</v>
+        <v>2515100</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.45</v>
+        <v>0.13</v>
       </c>
       <c r="H63" t="n">
-        <v>44.39</v>
+        <v>53.3</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3310,10 +3308,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.337</v>
+        <v>0.303</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.334</v>
+        <v>0.293</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3326,39 +3324,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.0738</v>
+        <v>3.51</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1720700</v>
+        <v>2386900</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.78</v>
+        <v>0.2</v>
       </c>
       <c r="H64" t="n">
-        <v>73.01000000000001</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.64</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.53</v>
+        <v>3.596</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.433</v>
+        <v>2.581</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3371,39 +3369,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0302</v>
+        <v>0.805</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.0387</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1656000</v>
+        <v>2383600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.14</v>
+        <v>0.93</v>
       </c>
       <c r="H65" t="n">
-        <v>53.09</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.56</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>3.598</v>
+        <v>0.765</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.581</v>
+        <v>0.744</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3416,39 +3414,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.805</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1612000</v>
+        <v>2322900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="H66" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.76</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.585</v>
+        <v>0.746</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.792</v>
+        <v>0.7</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3461,28 +3459,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.0063</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1603900</v>
+        <v>2273600</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.06</v>
+        <v>0.37</v>
       </c>
       <c r="H67" t="n">
-        <v>62.61</v>
+        <v>68.36</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3490,10 +3488,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.108</v>
+        <v>0.775</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.074</v>
+        <v>0.759</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3506,40 +3504,33 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.0156</v>
+        <v>0.0492</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1577500</v>
+        <v>2205000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H68" t="n">
-        <v>58.62</v>
+        <v>0.2</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J68" s="9" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="K68" s="9" t="n">
-        <v>0.593</v>
-      </c>
+      <c r="J68" s="9" t="n"/>
+      <c r="K68" s="9" t="n"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
     </row>
@@ -3551,39 +3542,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.0339</v>
+        <v>0.22</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1570500</v>
+        <v>2190300</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.58</v>
+        <v>0.1</v>
       </c>
       <c r="H69" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.5</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.111</v>
+        <v>0.23</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.123</v>
+        <v>0.245</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3596,39 +3587,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>0.0233</v>
+        <v>0.295</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1529900</v>
+        <v>2132500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="H70" t="n">
-        <v>58.61</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.03</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.256</v>
+        <v>0.29</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.168</v>
+        <v>0.278</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3650,19 +3641,19 @@
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1507100</v>
+        <v>2103000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H71" t="n">
-        <v>58.2</v>
+        <v>57.6</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3670,7 +3661,7 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.726</v>
+        <v>2.725</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>2.555</v>
@@ -3686,39 +3677,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0.0195</v>
+        <v>0.5</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1451200</v>
+        <v>2091500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="H72" t="n">
-        <v>56.67</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.49</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.57</v>
+        <v>0.585</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.553</v>
+        <v>0.792</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3731,39 +3722,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0</v>
+        <v>5.61</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1374400</v>
+        <v>2074200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.48</v>
+        <v>0.15</v>
       </c>
       <c r="H73" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.41</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.49</v>
+        <v>5.675</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2.055</v>
+        <v>5.248</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3776,39 +3767,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0086</v>
+        <v>2.81</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1330100</v>
+        <v>1989000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="H74" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.02</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>4.784</v>
+        <v>2.489</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>4.923</v>
+        <v>2.055</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3821,28 +3812,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1327300</v>
+        <v>1973600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="H75" t="n">
-        <v>26.55</v>
+        <v>66.58</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3850,10 +3841,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.54</v>
+        <v>0.239</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.579</v>
+        <v>0.214</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3866,28 +3857,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0134</v>
+        <v>0.405</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1297300</v>
+        <v>1868100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.09</v>
+        <v>0.77</v>
       </c>
       <c r="H76" t="n">
-        <v>45.31</v>
+        <v>54.94</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3895,10 +3886,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>2.269</v>
+        <v>0.4</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.213</v>
+        <v>0.384</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3911,39 +3902,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.495</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.2016</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1259500</v>
+        <v>1855900</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="H77" t="n">
-        <v>58.64</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>7.83</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.378</v>
+        <v>0.616</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.38</v>
+        <v>0.632</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3956,28 +3947,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>0</v>
+        <v>0.495</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1253400</v>
+        <v>1847700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.09</v>
+        <v>0.28</v>
       </c>
       <c r="H78" t="n">
-        <v>41.88</v>
+        <v>25.43</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3985,10 +3976,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.426</v>
+        <v>0.54</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.445</v>
+        <v>0.579</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4001,28 +3992,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>7.87</v>
+        <v>1.17</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>0.0396</v>
+        <v>0.0086</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1244300</v>
+        <v>1846900</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.33</v>
+        <v>1.22</v>
       </c>
       <c r="H79" t="n">
-        <v>73.53</v>
+        <v>61.49</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4030,10 +4021,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>6.876</v>
+        <v>1.107</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>6.621</v>
+        <v>1.074</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4046,39 +4037,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>0</v>
+        <v>4.7</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1225000</v>
+        <v>1835600</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="H80" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.6</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.896</v>
+        <v>4.784</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.856</v>
+        <v>4.923</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4091,28 +4082,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>3.08</v>
+        <v>0.645</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1182800</v>
+        <v>1826200</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H81" t="n">
-        <v>64.90000000000001</v>
+        <v>57.43</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4120,10 +4111,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.847</v>
+        <v>0.628</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.741</v>
+        <v>0.593</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4136,28 +4127,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EXSIMHB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.505</v>
+        <v>1.33</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.01</v>
+        <v>0.031</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1138400</v>
+        <v>1788200</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.75</v>
+        <v>0.45</v>
       </c>
       <c r="H82" t="n">
-        <v>62.2</v>
+        <v>59.39</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4165,10 +4156,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.497</v>
+        <v>1.257</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.471</v>
+        <v>1.168</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4181,28 +4172,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>5.3</v>
+        <v>0.655</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>0.0173</v>
+        <v>0.0155</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1133300</v>
+        <v>1727900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
       <c r="H83" t="n">
-        <v>40.52</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4210,10 +4201,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>5.587</v>
+        <v>0.637</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>5.734</v>
+        <v>0.604</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4226,28 +4217,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.645</v>
+        <v>2.62</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0403</v>
+        <v>0.0195</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1101700</v>
+        <v>1702700</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="H84" t="n">
-        <v>58.62</v>
+        <v>56.67</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4255,10 +4246,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.611</v>
+        <v>2.57</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.609</v>
+        <v>2.553</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4271,39 +4262,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.535</v>
+        <v>5.35</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.019</v>
+        <v>0.0269</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1100000</v>
+        <v>1675000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="H85" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.11</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.445</v>
+        <v>5.592</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.422</v>
+        <v>5.735</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4316,39 +4307,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>10.6</v>
+        <v>1.03</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.0134</v>
+        <v>0.03</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>971100</v>
+        <v>1592300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="H86" t="n">
-        <v>74.88</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.7</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>9.808</v>
+        <v>0.951</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>9.295</v>
+        <v>0.796</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4361,39 +4352,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.03</v>
+        <v>7.87</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.03</v>
+        <v>0.0396</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>964200</v>
+        <v>1557300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="H87" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.53</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.951</v>
+        <v>6.876</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.796</v>
+        <v>6.621</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4406,39 +4397,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>0</v>
+        <v>3.1</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>913500</v>
+        <v>1493300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.28</v>
+        <v>0.53</v>
       </c>
       <c r="H88" t="n">
-        <v>62.66</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.61</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.636</v>
+        <v>2.849</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.604</v>
+        <v>2.741</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4451,39 +4442,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.0052</v>
+        <v>0.5</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>883700</v>
+        <v>1478100</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.22</v>
+        <v>0.95</v>
       </c>
       <c r="H89" t="n">
-        <v>31.93</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.35</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.019</v>
+        <v>0.48</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.076</v>
+        <v>0.474</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4496,39 +4487,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>10.06</v>
+        <v>0.54</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.004</v>
+        <v>0.0286</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>873400</v>
+        <v>1455800</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H90" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.90000000000001</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>10.109</v>
+        <v>0.445</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>10.261</v>
+        <v>0.422</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4541,28 +4532,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.58</v>
+        <v>0.27</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>0.0488</v>
+        <v>0.0189</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>827100</v>
+        <v>1366700</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>73.03</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4570,10 +4561,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.306</v>
+        <v>0.249</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.084</v>
+        <v>0.256</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4586,39 +4577,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>EXSIMHB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.67</v>
+        <v>0.495</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.0074</v>
+        <v>-0.01</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>816300</v>
+        <v>1332500</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.21</v>
+        <v>2.04</v>
       </c>
       <c r="H92" t="n">
-        <v>69.42</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.8</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.562</v>
+        <v>0.497</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.214</v>
+        <v>0.471</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4631,39 +4622,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>0.0069</v>
+        <v>0.905</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>801000</v>
+        <v>1327300</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H93" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.03</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.771</v>
+        <v>0.896</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.831</v>
+        <v>0.856</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4676,39 +4667,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0183</v>
+        <v>0.865</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>791900</v>
+        <v>1318900</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.73</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.741</v>
+        <v>0.87</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4721,28 +4712,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.11</v>
+        <v>0.42</v>
       </c>
       <c r="E95" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>782600</v>
+        <v>1295000</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.12</v>
+        <v>1.13</v>
       </c>
       <c r="H95" t="n">
-        <v>42.97</v>
+        <v>41.88</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4750,10 +4741,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.152</v>
+        <v>0.426</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.157</v>
+        <v>0.445</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4766,28 +4757,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.19</v>
+        <v>0.48</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>725000</v>
+        <v>1274000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="H96" t="n">
-        <v>64.48</v>
+        <v>61.85</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4795,10 +4786,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.135</v>
+        <v>0.449</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.043</v>
+        <v>0.442</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4811,28 +4802,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>685000</v>
+        <v>1273400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="H97" t="n">
-        <v>61.79</v>
+        <v>57.64</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4840,10 +4831,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.481</v>
+        <v>0.611</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.474</v>
+        <v>0.609</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4856,39 +4847,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>652600</v>
+        <v>1259500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.05</v>
+        <v>1.35</v>
       </c>
       <c r="H98" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.64</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.345</v>
+        <v>0.378</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.303</v>
+        <v>0.38</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4901,28 +4892,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>0.0054</v>
+        <v>0.72</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>650300</v>
+        <v>1216200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="H99" t="n">
-        <v>36.99</v>
+        <v>28.63</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4930,10 +4921,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.926</v>
+        <v>0.77</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.049</v>
+        <v>0.831</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4946,28 +4937,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.74</v>
+        <v>10.06</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.0058</v>
+        <v>0.004</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>637300</v>
+        <v>1190200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H100" t="n">
-        <v>46.97</v>
+        <v>44.07</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4975,10 +4966,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.754</v>
+        <v>10.109</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.786</v>
+        <v>10.261</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4991,28 +4982,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.79</v>
+        <v>10.68</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.026</v>
+        <v>0.021</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>582400</v>
+        <v>1138100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.42</v>
+        <v>0.34</v>
       </c>
       <c r="H101" t="n">
-        <v>56.18</v>
+        <v>75.84</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5020,10 +5011,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.766</v>
+        <v>9.815</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.758</v>
+        <v>9.295999999999999</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5036,28 +5027,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.11</v>
+        <v>2.53</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.0091</v>
+        <v>0.0285</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>578100</v>
+        <v>1093800</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.12</v>
+        <v>0.7</v>
       </c>
       <c r="H102" t="n">
-        <v>75.45</v>
+        <v>71.16</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5065,10 +5056,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.019</v>
+        <v>2.301</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.852</v>
+        <v>2.083</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5081,28 +5072,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.19</v>
+        <v>0.285</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0165</v>
+        <v>-0.0172</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>566600</v>
+        <v>1043100</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H103" t="n">
-        <v>28.73</v>
+        <v>37.53</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5110,10 +5101,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.332</v>
+        <v>0.294</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.317</v>
+        <v>0.31</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5126,39 +5117,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.45</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>559400</v>
+        <v>1027200</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="H104" t="n">
-        <v>46.73</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.77</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.868</v>
+        <v>0.45</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.87</v>
+        <v>0.419</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5171,28 +5162,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>0.0135</v>
+        <v>1.45</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>549700</v>
+        <v>1003000</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H105" t="n">
-        <v>50.36</v>
+        <v>43.49</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5200,10 +5191,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>5.228</v>
+        <v>1.466</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>5.286</v>
+        <v>1.47</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5216,39 +5207,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.63</v>
+        <v>0.975</v>
       </c>
       <c r="E106" s="15" t="n">
-        <v>0.0328</v>
+        <v>0.0052</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>535200</v>
+        <v>995300</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="H106" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.93</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.553</v>
+        <v>1.019</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.533</v>
+        <v>1.076</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5261,28 +5252,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>3.12</v>
+        <v>0.835</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.0183</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>523400</v>
+        <v>927300</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="H107" t="n">
-        <v>35.75</v>
+        <v>59.26</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5290,10 +5281,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>3.222</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>3.426</v>
+        <v>0.741</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5306,28 +5297,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.0132</v>
+        <v>2.59</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>518000</v>
+        <v>890000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H108" t="n">
-        <v>66.51000000000001</v>
+        <v>40.18</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5335,10 +5326,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.71</v>
+        <v>2.654</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.641</v>
+        <v>2.823</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5351,28 +5342,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WCEHB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>506700</v>
+        <v>879800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="H109" t="n">
-        <v>45.63</v>
+        <v>28.73</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5380,16 +5371,1501 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.702</v>
+        <v>1.332</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.694</v>
+        <v>1.317</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>871900</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H110" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>849400</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H111" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>843600</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H112" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>833200</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H113" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>832400</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H114" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>818600</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H115" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>808800</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>756900</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H117" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>1.926</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>749200</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H118" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>734500</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H119" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>733500</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>732300</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H121" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>5.233</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>5.287</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>718400</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H122" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7174</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CAB</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>710200</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H123" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>678600</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H124" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>656600</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H125" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>3.812</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>3.496</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>627700</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H126" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>625800</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H127" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>13.097</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>WCEHB</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>616700</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H128" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>615900</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H129" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>614200</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H130" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>5.003</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>5.049</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>593000</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H131" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>3.426</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>583400</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H132" t="n">
+        <v>53.06</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>578200</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>572000</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H134" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>2.955</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>570000</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H135" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>568000</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H136" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>561400</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H137" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>7.779</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>553600</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H138" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>7.767</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>7.751</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>550600</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H139" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5280</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>KIPREIT</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>542500</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H140" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>525400</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H141" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>2.054</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>2.092</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>514500</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H142" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M109"/>
+  <autoFilter ref="A1:M142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
+++ b/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-05" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,95 +557,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1005700</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多，但RSI达75.45已超买，现价高于50日均线约30%，信号可靠性偏弱。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>7106</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>SUPERMX</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.0357</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>8828600</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>65.20999999999999</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>10557600</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.393</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.334</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多，现价0.435高于50日均线0.334约30%，RSI 65.21接近超买区，信号偏强但需留意短线过热。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>-0.3913</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>560004700</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，现价0.44高于50日均线0.334，RSI 66.1接近超买区，信号偏强但需留意高位风险。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,39 +663,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.0862</v>
+        <v>0.075</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-0.3478</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>86667100</v>
+        <v>687664200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>2.23</v>
+        <v>1.4</v>
       </c>
       <c r="H4" t="n">
-        <v>75.66</v>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>15.25</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.251</v>
+        <v>0.219</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.236</v>
+        <v>0.436</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,39 +708,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.2</v>
+        <v>0.32</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.1034</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>40469500</v>
+        <v>87998400</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="H5" t="n">
-        <v>26.88</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.48</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.055</v>
+        <v>0.252</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.073</v>
+        <v>0.236</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,28 +753,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-0.2857</v>
+        <v>-0.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>31241600</v>
+        <v>41219500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>5.62</v>
+        <v>1.77</v>
       </c>
       <c r="H6" t="n">
-        <v>37.22</v>
+        <v>26.88</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,10 +782,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.197</v>
+        <v>0.055</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.176</v>
+        <v>0.073</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +798,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0461</v>
+        <v>0.155</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.2619</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>23194200</v>
+        <v>35111000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.5</v>
+        <v>6.32</v>
       </c>
       <c r="H7" t="n">
-        <v>63.54</v>
+        <v>38.28</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +827,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.744</v>
+        <v>0.197</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.145</v>
+        <v>0.795</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.0741</v>
+        <v>0.0461</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>17682800</v>
+        <v>27355700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>4.36</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="n">
-        <v>81.98</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.54</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.101</v>
+        <v>0.744</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.089</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +888,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0097</v>
+        <v>1.88</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.0273</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>15033900</v>
+        <v>18911400</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="H9" t="n">
-        <v>62.93</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.72</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.479</v>
+        <v>1.765</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.475</v>
+        <v>1.589</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +933,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1.86</v>
+        <v>0.15</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.1111</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>13895700</v>
+        <v>18363600</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.63</v>
+        <v>4.53</v>
       </c>
       <c r="H10" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.04000000000001</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.763</v>
+        <v>0.101</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1.589</v>
+        <v>0.089</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +978,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>-0.0083</v>
+        <v>-0.0097</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>13861000</v>
+        <v>16308800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="n">
-        <v>70.97</v>
+        <v>62.93</v>
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
@@ -999,10 +1007,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.479</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.498</v>
+        <v>0.475</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1023,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.0284</v>
+        <v>0.595</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>13747200</v>
+        <v>15055300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.25</v>
+        <v>0.58</v>
       </c>
       <c r="H12" t="n">
-        <v>68.09999999999999</v>
+        <v>68.09</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1044,10 +1052,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.65</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.591</v>
+        <v>0.497</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1068,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.0379</v>
+        <v>0.73</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.0355</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>12417400</v>
+        <v>14780600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.65</v>
+        <v>1.34</v>
       </c>
       <c r="H13" t="n">
-        <v>66.18000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1089,10 +1097,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.555</v>
+        <v>0.651</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.5</v>
+        <v>0.591</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1113,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.027</v>
+        <v>0.645</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>12257100</v>
+        <v>13488200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="H14" t="n">
-        <v>70.89</v>
+        <v>68.38</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -1134,10 +1142,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.344</v>
+        <v>0.556</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.215</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,28 +1158,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0405</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12014800</v>
+        <v>13331400</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="H15" t="n">
-        <v>64.31</v>
+        <v>71.78</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1179,10 +1187,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.162</v>
+        <v>0.344</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.126</v>
+        <v>0.215</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1210,10 +1218,10 @@
         <v>0.0435</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11775800</v>
+        <v>12506100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
@@ -1233,28 +1241,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0727</v>
+        <v>0.18</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9845900</v>
+        <v>12460400</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
       <c r="H17" t="n">
-        <v>57.83</v>
+        <v>64.31</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1262,10 +1270,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.271</v>
+        <v>0.162</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.307</v>
+        <v>0.126</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,28 +1286,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0727</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8656600</v>
+        <v>11670600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="H18" t="n">
-        <v>66.31</v>
+        <v>57.83</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1307,10 +1315,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.507</v>
+        <v>0.271</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.424</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,12 +1331,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0043</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MTRONIC</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
@@ -1338,25 +1346,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8140000</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="H19" t="n">
-        <v>46.51</v>
-      </c>
+        <v>10109300</v>
+      </c>
+      <c r="G19" s="12" t="n"/>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0.006</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1368,28 +1367,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8054100</v>
+        <v>9682200</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.25</v>
+        <v>0.63</v>
       </c>
       <c r="H20" t="n">
-        <v>68.81</v>
+        <v>65.02</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1397,10 +1396,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.707</v>
+        <v>0.507</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.632</v>
+        <v>0.424</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,39 +1412,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.1053</v>
+        <v>0.165</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7252500</v>
+        <v>9105700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2.21</v>
+        <v>0.22</v>
       </c>
       <c r="H21" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.39</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.098</v>
+        <v>0.147</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1458,31 +1457,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>5.01</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0176</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7087300</v>
-      </c>
-      <c r="G22" s="12" t="n"/>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+        <v>8873300</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H22" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>4.876</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>4.596</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1494,28 +1502,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>0.78</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.06849999999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6550900</v>
+        <v>8798200</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="H23" t="n">
-        <v>68.88</v>
+        <v>68.23</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1523,10 +1531,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.284</v>
+        <v>0.707</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.272</v>
+        <v>0.632</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,39 +1547,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0043</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>MTRONIC</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.1111</v>
+        <v>0.005</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6123600</v>
+        <v>8140000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.62</v>
+        <v>14.95</v>
       </c>
       <c r="H24" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.035</v>
+        <v>0.006</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.033</v>
+        <v>0.006</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,39 +1592,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0137</v>
+        <v>0.105</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.1053</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5812200</v>
+        <v>7867500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.24</v>
+        <v>2.4</v>
       </c>
       <c r="H25" t="n">
-        <v>63.51</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.09</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>4.878</v>
+        <v>0.1</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4.596</v>
+        <v>0.098</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,39 +1637,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.39</v>
+        <v>0.04</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>-0.025</v>
+        <v>-0.1111</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5555800</v>
+        <v>6913600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.2</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.405</v>
+        <v>0.035</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.411</v>
+        <v>0.033</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1682,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.39</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5267500</v>
+        <v>6859600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.13</v>
+        <v>0.6</v>
       </c>
       <c r="H27" t="n">
-        <v>56.66</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.03</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.16</v>
+        <v>0.405</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.147</v>
+        <v>0.411</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,36 +1727,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0189</v>
+        <v>0.295</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5109400</v>
+        <v>6759700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.39</v>
+        <v>1.08</v>
       </c>
       <c r="H28" t="n">
-        <v>27.8</v>
+        <v>63.18</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+      <c r="J28" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.272</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1760,28 +1772,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.0141</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4908800</v>
+        <v>6475100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="H29" t="n">
-        <v>64.34</v>
+        <v>53.15</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1789,10 +1801,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.339</v>
+        <v>0.774</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.319</v>
+        <v>0.775</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1805,39 +1817,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0.0127</v>
+        <v>0.805</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4888400</v>
+        <v>6423800</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0.43</v>
       </c>
       <c r="H30" t="n">
-        <v>66.31</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.89</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.38</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.373</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1850,28 +1862,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0367</v>
+        <v>0.49</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.0297</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4885200</v>
+        <v>5554200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
       <c r="H31" t="n">
-        <v>76.83</v>
+        <v>25.62</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1879,10 +1891,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.041</v>
+        <v>0.584</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.884</v>
+        <v>0.792</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1895,28 +1907,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4820400</v>
+        <v>5536000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="H32" t="n">
-        <v>50.21</v>
+        <v>40.9</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1924,10 +1936,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.102</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>2.072</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1940,40 +1952,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.0385</v>
+        <v>0.265</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4720800</v>
+        <v>5474900</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H33" t="n">
-        <v>53.09</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>1.028</v>
-      </c>
+        <v>25.81</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
     </row>
@@ -1985,28 +1993,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.78</v>
+        <v>0.36</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0141</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4595000</v>
+        <v>5348300</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.33</v>
+        <v>0.72</v>
       </c>
       <c r="H34" t="n">
-        <v>53.15</v>
+        <v>64.34</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2014,10 +2022,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.774</v>
+        <v>0.339</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.775</v>
+        <v>0.319</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2030,33 +2038,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4522600</v>
+        <v>5283900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
+      </c>
+      <c r="H35" t="n">
+        <v>66.31</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
+      <c r="J35" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.373</v>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
     </row>
@@ -2068,28 +2083,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>BINTAI</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.075</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4145200</v>
+        <v>5211200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>4.15</v>
+        <v>1.97</v>
       </c>
       <c r="H36" t="n">
-        <v>64.01000000000001</v>
+        <v>55.79</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2097,10 +2112,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.68</v>
+        <v>0.074</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.679</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2113,39 +2128,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.445</v>
+        <v>1.13</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>0.023</v>
+        <v>0.0367</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4134600</v>
+        <v>5120700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="H37" t="n">
-        <v>60.74</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>76.83</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.411</v>
+        <v>1.041</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.407</v>
+        <v>0.884</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2158,28 +2173,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.38</v>
+        <v>0.445</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.023</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4036700</v>
+        <v>4972800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.48</v>
+        <v>0.84</v>
       </c>
       <c r="H38" t="n">
-        <v>74</v>
+        <v>60.74</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2187,10 +2202,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.342</v>
+        <v>0.411</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.315</v>
+        <v>0.407</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2218,10 +2233,10 @@
         <v>0.007800000000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3998200</v>
+        <v>4955700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H39" t="n">
         <v>53.96</v>
@@ -2248,36 +2263,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.275</v>
+        <v>1.08</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.0385</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3900400</v>
+        <v>4934600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="H40" t="n">
-        <v>18.18</v>
+        <v>53.09</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
+      <c r="J40" s="9" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>1.028</v>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
     </row>
@@ -2289,28 +2308,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>-0.0213</v>
+        <v>0.38</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3818700</v>
+        <v>4607700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.13</v>
+        <v>0.55</v>
       </c>
       <c r="H41" t="n">
-        <v>29.3</v>
+        <v>74</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2318,10 +2337,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.261</v>
+        <v>0.342</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.314</v>
+        <v>0.315</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2334,40 +2353,33 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.08470000000000001</v>
+        <v>0.475</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3619300</v>
+        <v>4534700</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="H42" t="n">
-        <v>71.66</v>
+        <v>0.31</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J42" s="9" t="n">
-        <v>1.116</v>
-      </c>
-      <c r="K42" s="9" t="n">
-        <v>1.124</v>
-      </c>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
     </row>
@@ -2379,28 +2391,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.27</v>
+        <v>0.735</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3445200</v>
+        <v>4400800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.49</v>
+        <v>4.41</v>
       </c>
       <c r="H43" t="n">
-        <v>76.95</v>
+        <v>62.56</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2408,10 +2420,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.017</v>
+        <v>0.679</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.788</v>
+        <v>0.679</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2424,28 +2436,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.04480000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.04</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3367800</v>
+        <v>4316800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.87</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="n">
-        <v>38.57</v>
+        <v>52.91</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2453,10 +2465,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.336</v>
+        <v>0.383</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.334</v>
+        <v>0.39</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2469,40 +2481,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3307900</v>
+        <v>4262600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H45" t="n">
-        <v>32.23</v>
+        <v>20.04</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J45" s="9" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>0.208</v>
-      </c>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
     </row>
@@ -2514,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.705</v>
+        <v>0.305</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>0.0071</v>
+        <v>0.0167</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3307700</v>
+        <v>4250100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.49</v>
+        <v>0.22</v>
       </c>
       <c r="H46" t="n">
-        <v>54.98</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.3</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.303</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.67</v>
+        <v>0.293</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2559,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.785</v>
+        <v>1.3</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0397</v>
+        <v>0.1017</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3269000</v>
+        <v>4237300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.51</v>
+        <v>1.58</v>
       </c>
       <c r="H47" t="n">
-        <v>57.93</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.97</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.77</v>
+        <v>1.118</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.771</v>
+        <v>1.125</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2604,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.1143</v>
+        <v>0.15</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3236200</v>
+        <v>4178100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
       <c r="H48" t="n">
-        <v>69.47</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.36</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.165</v>
+        <v>0.172</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.165</v>
+        <v>0.208</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2649,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.0464</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3211400</v>
+        <v>4005600</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.46</v>
+        <v>0.62</v>
       </c>
       <c r="H49" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.86</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.531</v>
+        <v>0.77</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.433</v>
+        <v>0.771</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2694,28 +2702,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.235</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3153100</v>
+        <v>3933300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.41</v>
+        <v>0.14</v>
       </c>
       <c r="H50" t="n">
-        <v>69.67</v>
+        <v>30.7</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2723,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>3.835</v>
+        <v>0.261</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>3.348</v>
+        <v>0.314</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2739,28 +2747,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>0.027</v>
+        <v>2.21</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0134</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3114700</v>
+        <v>3722800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H51" t="n">
-        <v>48.79</v>
+        <v>45.31</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2768,10 +2776,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.194</v>
+        <v>2.269</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.181</v>
+        <v>2.213</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2784,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.19</v>
+        <v>4.25</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>0.0348</v>
+        <v>0.0192</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3102900</v>
+        <v>3712400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="H52" t="n">
-        <v>56.49</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.67</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.157</v>
+        <v>3.835</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>1.111</v>
+        <v>3.348</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2829,28 +2837,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>0</v>
+        <v>0.71</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3046400</v>
+        <v>3707300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H53" t="n">
-        <v>61.02</v>
+        <v>55.83</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2858,10 +2866,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.579</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.577</v>
+        <v>0.67</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2874,39 +2882,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.335</v>
+        <v>0.195</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.0152</v>
+        <v>0.0541</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3017500</v>
+        <v>3644400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.53</v>
+        <v>0.16</v>
       </c>
       <c r="H54" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.1</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.322</v>
+        <v>0.195</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.338</v>
+        <v>0.181</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2919,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>2.21</v>
+        <v>0.32</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.0134</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2997400</v>
+        <v>3637400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>45.31</v>
+        <v>38.57</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2948,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>2.269</v>
+        <v>0.336</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2.213</v>
+        <v>0.334</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2964,39 +2972,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0049</v>
+        <v>1.26</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2889000</v>
+        <v>3614200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="H56" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.56999999999999</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.103</v>
+        <v>1.016</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.073</v>
+        <v>0.788</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3009,39 +3017,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.0179</v>
+        <v>0.335</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2841400</v>
+        <v>3598100</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.37</v>
+        <v>0.64</v>
       </c>
       <c r="H57" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.265</v>
+        <v>0.322</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.227</v>
+        <v>0.338</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3054,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.575</v>
+        <v>0.195</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.1143</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2829800</v>
+        <v>3597500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H58" t="n">
-        <v>67.37</v>
+        <v>69.47</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3083,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.526</v>
+        <v>0.165</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.48</v>
+        <v>0.165</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3099,39 +3107,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.61</v>
+        <v>1.19</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.0348</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2820900</v>
+        <v>3351800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="H59" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.49</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.607</v>
+        <v>1.157</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.608</v>
+        <v>1.111</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3144,39 +3152,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.66</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.08199999999999999</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2636300</v>
+        <v>3340500</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>3.67</v>
+        <v>1.52</v>
       </c>
       <c r="H60" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.40000000000001</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.272</v>
+        <v>0.531</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.327</v>
+        <v>0.433</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3189,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0634</v>
+        <v>2.18</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>-0.0522</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2607300</v>
+        <v>3337600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.78</v>
+        <v>4.65</v>
       </c>
       <c r="H61" t="n">
-        <v>74.70999999999999</v>
+        <v>42.22</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3218,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2.498</v>
+        <v>2.275</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.917</v>
+        <v>2.328</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3234,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.51</v>
+        <v>0.865</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>-0.0097</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2533300</v>
+        <v>3307900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
       <c r="H62" t="n">
-        <v>46</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.73</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.52</v>
+        <v>0.868</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.531</v>
+        <v>0.87</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3279,39 +3287,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.305</v>
+        <v>0.61</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.0083</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2515100</v>
+        <v>3177000</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="H63" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.33</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.303</v>
+        <v>0.607</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.293</v>
+        <v>0.608</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3324,28 +3332,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0357</v>
+        <v>3</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0563</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2386900</v>
+        <v>3134400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H64" t="n">
-        <v>52.64</v>
+        <v>74.36</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3353,10 +3361,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>3.596</v>
+        <v>2.496</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2.581</v>
+        <v>1.917</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3369,39 +3377,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>0.0387</v>
+        <v>0.495</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2383600</v>
+        <v>3097600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.93</v>
+        <v>0.47</v>
       </c>
       <c r="H65" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.43</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.765</v>
+        <v>0.54</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.744</v>
+        <v>0.579</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3414,28 +3422,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.805</v>
+        <v>0.62</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.0126</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2322900</v>
+        <v>3076800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.19</v>
+        <v>1.01</v>
       </c>
       <c r="H66" t="n">
-        <v>62.76</v>
+        <v>62.03</v>
       </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
@@ -3443,10 +3451,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.746</v>
+        <v>0.579</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.7</v>
+        <v>0.577</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3459,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0063</v>
+        <v>0.0175</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2273600</v>
+        <v>3013700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="H67" t="n">
-        <v>68.36</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3488,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.775</v>
+        <v>0.526</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.759</v>
+        <v>0.48</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3504,33 +3512,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.0492</v>
+        <v>0.0063</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2205000</v>
+        <v>3012700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
+      </c>
+      <c r="H68" t="n">
+        <v>62.13</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J68" s="9" t="n"/>
-      <c r="K68" s="9" t="n"/>
+      <c r="J68" s="9" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
     </row>
@@ -3542,28 +3557,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.22</v>
+        <v>0.515</v>
       </c>
       <c r="E69" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2190300</v>
+        <v>2966500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="H69" t="n">
-        <v>40.5</v>
+        <v>47.66</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3571,10 +3586,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.245</v>
+        <v>0.532</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3587,39 +3602,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.295</v>
+        <v>0.275</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>-0.0167</v>
+        <v>-0.0179</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2132500</v>
+        <v>2891400</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="H70" t="n">
-        <v>53.03</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.67</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.29</v>
+        <v>0.265</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.278</v>
+        <v>0.227</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3632,39 +3647,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.82</v>
+        <v>5.6</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>-0.0035</v>
+        <v>-0.0141</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2103000</v>
+        <v>2771200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="H71" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.725</v>
+        <v>5.674</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.555</v>
+        <v>5.248</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3677,39 +3692,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2091500</v>
+        <v>2736700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.05</v>
+        <v>1.07</v>
       </c>
       <c r="H72" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.66</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.585</v>
+        <v>0.764</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.792</v>
+        <v>0.743</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3722,40 +3737,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>-0.0123</v>
+        <v>0.315</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2074200</v>
+        <v>2730500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H73" t="n">
-        <v>50.41</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="n">
-        <v>5.675</v>
-      </c>
-      <c r="K73" s="9" t="n">
-        <v>5.248</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n"/>
+      <c r="K73" s="9" t="n"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3767,39 +3775,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.81</v>
+        <v>3.53</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>-0.0071</v>
+        <v>-0.0302</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1989000</v>
+        <v>2714700</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.7</v>
+        <v>0.23</v>
       </c>
       <c r="H74" t="n">
-        <v>74.02</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.09</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.489</v>
+        <v>3.598</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.055</v>
+        <v>2.581</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3812,39 +3820,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.265</v>
+        <v>2.85</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.0071</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1973600</v>
+        <v>2655000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="H75" t="n">
-        <v>66.58</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.07</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.239</v>
+        <v>2.728</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.214</v>
+        <v>2.556</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3857,39 +3865,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0</v>
+        <v>0.805</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1868100</v>
+        <v>2556600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.77</v>
+        <v>0.41</v>
       </c>
       <c r="H76" t="n">
-        <v>54.94</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.09999999999999</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.4</v>
+        <v>0.776</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.384</v>
+        <v>0.759</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3902,39 +3910,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.2016</v>
+        <v>2.65</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0311</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1855900</v>
+        <v>2524200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>1.83</v>
+        <v>0.47</v>
       </c>
       <c r="H77" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.5</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.616</v>
+        <v>2.572</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.632</v>
+        <v>2.553</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3947,28 +3955,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.01</v>
+        <v>0.265</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1847700</v>
+        <v>2420100</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.28</v>
+        <v>0.71</v>
       </c>
       <c r="H78" t="n">
-        <v>25.43</v>
+        <v>66.58</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3976,10 +3984,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.54</v>
+        <v>0.239</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.579</v>
+        <v>0.214</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -3992,28 +4000,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.0086</v>
+        <v>2.81</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1846900</v>
+        <v>2397000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="H79" t="n">
-        <v>61.49</v>
+        <v>74.02</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4021,10 +4029,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.107</v>
+        <v>2.489</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.074</v>
+        <v>2.055</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4037,28 +4045,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0086</v>
+        <v>0.22</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1835600</v>
+        <v>2292400</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0.11</v>
       </c>
       <c r="H80" t="n">
-        <v>35.6</v>
+        <v>40.5</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4066,10 +4074,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>4.784</v>
+        <v>0.23</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>4.923</v>
+        <v>0.245</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4082,28 +4090,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.645</v>
+        <v>3.18</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0392</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1826200</v>
+        <v>2265600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>57.43</v>
+        <v>68.19</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4111,10 +4119,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.628</v>
+        <v>2.857</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.593</v>
+        <v>2.743</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4127,39 +4135,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0.031</v>
+        <v>0.3</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1788200</v>
+        <v>2244600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.45</v>
+        <v>0.14</v>
       </c>
       <c r="H82" t="n">
-        <v>59.39</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.88</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.257</v>
+        <v>0.29</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.168</v>
+        <v>0.278</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4172,28 +4180,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.655</v>
+        <v>0.37</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>0.0155</v>
+        <v>0.0137</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1727900</v>
+        <v>2237400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="H83" t="n">
-        <v>67.59999999999999</v>
+        <v>53.25</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4201,10 +4209,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.637</v>
+        <v>0.367</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.604</v>
+        <v>0.367</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4217,39 +4225,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2.62</v>
+        <v>0.46</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0195</v>
+        <v>0.0222</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1702700</v>
+        <v>2203000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="H84" t="n">
-        <v>56.67</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.3</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.57</v>
+        <v>0.451</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.553</v>
+        <v>0.419</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4262,28 +4270,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>5.35</v>
+        <v>4.7</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.0269</v>
+        <v>0.0086</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1675000</v>
+        <v>2125700</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="H85" t="n">
-        <v>42.11</v>
+        <v>35.6</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4291,10 +4299,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>5.592</v>
+        <v>4.784</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>5.735</v>
+        <v>4.923</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4307,39 +4315,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1592300</v>
+        <v>2086000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.19</v>
+        <v>1.13</v>
       </c>
       <c r="H86" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.89</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.951</v>
+        <v>0.91</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.796</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4361,19 +4369,19 @@
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>7.87</v>
+        <v>7.93</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.0396</v>
+        <v>0.0476</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1557300</v>
+        <v>2060200</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="H87" t="n">
-        <v>73.53</v>
+        <v>74.17</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4381,10 +4389,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>6.876</v>
+        <v>6.881</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>6.621</v>
+        <v>6.622</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4397,39 +4405,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>3.1</v>
+        <v>1.34</v>
       </c>
       <c r="E88" s="15" t="n">
-        <v>0.0131</v>
+        <v>0.0388</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1493300</v>
+        <v>2052800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H88" t="n">
-        <v>65.61</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.14</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.849</v>
+        <v>1.258</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.741</v>
+        <v>1.168</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4442,39 +4450,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.41</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1478100</v>
+        <v>2040600</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="H89" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.25</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.48</v>
+        <v>0.401</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.474</v>
+        <v>0.384</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4487,28 +4495,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.54</v>
+        <v>1.19</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.0286</v>
+        <v>0.0259</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1455800</v>
+        <v>2012600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.49</v>
+        <v>1.33</v>
       </c>
       <c r="H90" t="n">
-        <v>79.90000000000001</v>
+        <v>63.67</v>
       </c>
       <c r="I90" s="16" t="inlineStr">
         <is>
@@ -4516,10 +4524,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.445</v>
+        <v>1.109</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.422</v>
+        <v>1.074</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4532,39 +4540,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.0189</v>
+        <v>0.23</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1366700</v>
+        <v>2005200</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H91" t="n">
-        <v>66.98999999999999</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.87</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.249</v>
+        <v>0.25</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.256</v>
+        <v>0.253</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4577,28 +4585,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EXSIMHB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.01</v>
+        <v>5.35</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.0269</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1332500</v>
+        <v>2000500</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>2.04</v>
+        <v>0.6</v>
       </c>
       <c r="H92" t="n">
-        <v>52.8</v>
+        <v>42.11</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4606,10 +4614,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.497</v>
+        <v>5.592</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.471</v>
+        <v>5.735</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4622,28 +4630,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1327300</v>
+        <v>1947700</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="H93" t="n">
-        <v>57.03</v>
+        <v>57.43</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4651,10 +4659,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.896</v>
+        <v>0.628</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.856</v>
+        <v>0.593</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4667,28 +4675,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.475</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1318900</v>
+        <v>1935800</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="H94" t="n">
-        <v>46.73</v>
+        <v>58.92</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4696,10 +4704,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.868</v>
+        <v>0.452</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.87</v>
+        <v>0.459</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4712,28 +4720,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.1935</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1295000</v>
+        <v>1880300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="H95" t="n">
-        <v>41.88</v>
+        <v>8.08</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4741,10 +4749,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.426</v>
+        <v>0.616</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.445</v>
+        <v>0.633</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4757,28 +4765,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.0105</v>
+        <v>0.0286</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1274000</v>
+        <v>1870800</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="H96" t="n">
-        <v>61.85</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4786,10 +4794,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.449</v>
+        <v>0.445</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.442</v>
+        <v>0.422</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4802,39 +4810,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.64</v>
+        <v>0.655</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.0323</v>
+        <v>0.0155</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1273400</v>
+        <v>1867200</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
       </c>
       <c r="H97" t="n">
-        <v>57.64</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.611</v>
+        <v>0.637</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.609</v>
+        <v>0.604</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4847,39 +4855,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0398</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GDGROUP</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.385</v>
+        <v>1.02</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.02</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1259500</v>
+        <v>1865200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>1.35</v>
+        <v>0.22</v>
       </c>
       <c r="H98" t="n">
-        <v>58.64</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.81</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.378</v>
+        <v>0.95</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.38</v>
+        <v>0.796</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4892,39 +4900,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1216200</v>
+        <v>1860900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
       <c r="H99" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.79000000000001</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.77</v>
+        <v>2.56</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.831</v>
+        <v>2.214</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4937,39 +4945,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>10.06</v>
+        <v>0.27</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.004</v>
+        <v>0.0189</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1190200</v>
+        <v>1824800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.1</v>
+        <v>0.92</v>
       </c>
       <c r="H100" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.98999999999999</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>10.109</v>
+        <v>0.249</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>10.261</v>
+        <v>0.256</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4991,19 +4999,19 @@
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>10.68</v>
+        <v>10.78</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.021</v>
+        <v>0.0306</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1138100</v>
+        <v>1814600</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.34</v>
+        <v>0.55</v>
       </c>
       <c r="H101" t="n">
-        <v>75.84</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5011,10 +5019,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>9.815</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>9.295999999999999</v>
+        <v>9.298</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5027,28 +5035,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.53</v>
+        <v>0.76</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.0285</v>
+        <v>0.0066</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1093800</v>
+        <v>1670100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="H102" t="n">
-        <v>71.16</v>
+        <v>65.78</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5056,10 +5064,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.301</v>
+        <v>0.71</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.083</v>
+        <v>0.641</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5072,39 +5080,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.285</v>
+        <v>0.5</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0172</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1043100</v>
+        <v>1659000</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.16</v>
+        <v>1.07</v>
       </c>
       <c r="H103" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.35</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.294</v>
+        <v>0.48</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.31</v>
+        <v>0.474</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5117,39 +5125,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.0254</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1027200</v>
+        <v>1562100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="H104" t="n">
-        <v>51.77</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.83</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.45</v>
+        <v>1.137</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.419</v>
+        <v>1.043</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5162,39 +5170,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1003000</v>
+        <v>1504100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="H105" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.64</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.466</v>
+        <v>0.611</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.47</v>
+        <v>0.609</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5207,28 +5215,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.975</v>
+        <v>0.725</v>
       </c>
       <c r="E106" s="15" t="n">
-        <v>0.0052</v>
+        <v>0.0069</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>995300</v>
+        <v>1450300</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H106" t="n">
-        <v>31.93</v>
+        <v>30.77</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5236,10 +5244,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.019</v>
+        <v>0.771</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.076</v>
+        <v>0.831</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5252,28 +5260,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>0.0183</v>
+        <v>0.205</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.08890000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>927300</v>
+        <v>1396600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.3</v>
+        <v>0.74</v>
       </c>
       <c r="H107" t="n">
-        <v>59.26</v>
+        <v>33.09</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5281,10 +5289,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.741</v>
+        <v>0.241</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5297,39 +5305,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0</v>
+        <v>10.08</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.006</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>890000</v>
+        <v>1391000</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>0.12</v>
       </c>
       <c r="H108" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.52</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.654</v>
+        <v>10.111</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.823</v>
+        <v>10.261</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5342,39 +5350,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0165</v>
+        <v>0.48</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>879800</v>
+        <v>1357100</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H109" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.85</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.332</v>
+        <v>0.449</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.317</v>
+        <v>0.442</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5387,39 +5395,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.77</v>
+        <v>1.29</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>-0.0142</v>
+        <v>-0.0077</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>871900</v>
+        <v>1351600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H110" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.43</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.792</v>
+        <v>1.344</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.675</v>
+        <v>1.302</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5432,39 +5440,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>EXSIMHB</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>0</v>
+        <v>0.495</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>849400</v>
+        <v>1332500</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.18</v>
+        <v>2.04</v>
       </c>
       <c r="H111" t="n">
-        <v>74.51000000000001</v>
-      </c>
-      <c r="I111" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.8</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.018</v>
+        <v>0.497</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.851</v>
+        <v>0.471</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5477,39 +5485,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>-0.0058</v>
+        <v>0.905</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>843600</v>
+        <v>1327300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H112" t="n">
-        <v>44.34</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.03</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.752</v>
+        <v>0.896</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.786</v>
+        <v>0.856</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5522,39 +5530,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0149</v>
+        <v>0.42</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>833200</v>
+        <v>1300100</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.22</v>
+        <v>1.13</v>
       </c>
       <c r="H113" t="n">
-        <v>66.79000000000001</v>
-      </c>
-      <c r="I113" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.88</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.56</v>
+        <v>0.426</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.214</v>
+        <v>0.445</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5567,39 +5575,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0398</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GDGROUP</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>832400</v>
+        <v>1279500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.12</v>
+        <v>1.37</v>
       </c>
       <c r="H114" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.64</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.151</v>
+        <v>0.378</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.157</v>
+        <v>0.38</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5612,39 +5620,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.785</v>
+        <v>0.835</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>0.0195</v>
+        <v>0.0183</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>818600</v>
+        <v>1279200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="H115" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.26</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.765</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.758</v>
+        <v>0.741</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5657,28 +5665,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0090</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>ELSOFT</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.2</v>
+        <v>0.29</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.0175</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>808800</v>
+        <v>1276800</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.2</v>
+        <v>2.72</v>
       </c>
       <c r="H116" t="n">
-        <v>65.7</v>
+        <v>62.48</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5686,10 +5694,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>1.136</v>
+        <v>0.265</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1.043</v>
+        <v>0.266</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5702,28 +5710,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0</v>
+        <v>0.975</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>756900</v>
+        <v>1255100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H117" t="n">
-        <v>35.09</v>
+        <v>31.93</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5731,10 +5739,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.926</v>
+        <v>1.019</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.049</v>
+        <v>1.076</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5747,39 +5755,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="E118" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>749200</v>
+        <v>1244000</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
       <c r="H118" t="n">
-        <v>53.88</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.97</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.908</v>
+        <v>1.152</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>1.157</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5792,28 +5800,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.765</v>
+        <v>2.55</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.0366</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>734500</v>
+        <v>1221500</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.12</v>
+        <v>0.78</v>
       </c>
       <c r="H119" t="n">
-        <v>66.51000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
@@ -5821,10 +5829,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.71</v>
+        <v>2.303</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.641</v>
+        <v>2.083</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5837,28 +5845,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.018</v>
+        <v>1</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>733500</v>
+        <v>1183400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.2</v>
+        <v>0.54</v>
       </c>
       <c r="H120" t="n">
-        <v>37.54</v>
+        <v>22.28</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5866,10 +5874,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.077</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.588</v>
+        <v>1.136</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5882,39 +5890,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>0.0232</v>
+        <v>2.77</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>732300</v>
+        <v>1176200</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.31</v>
+        <v>0.09</v>
       </c>
       <c r="H121" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.45</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>5.233</v>
+        <v>2.792</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>5.287</v>
+        <v>2.675</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5927,39 +5935,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>1.73</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>718400</v>
+        <v>1140000</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H122" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.54</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.255</v>
+        <v>1.753</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.294</v>
+        <v>1.786</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5972,28 +5980,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.625</v>
+        <v>0.785</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>0.0246</v>
+        <v>0.0195</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>710200</v>
+        <v>1130100</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>86.84999999999999</v>
+        <v>55.19</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6001,10 +6009,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.552</v>
+        <v>0.765</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.533</v>
+        <v>0.758</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6017,28 +6025,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0077</v>
+        <v>0.33</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>678600</v>
+        <v>1088200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H124" t="n">
-        <v>43.43</v>
+        <v>31.85</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6046,10 +6054,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.344</v>
+        <v>0.344</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.302</v>
+        <v>0.348</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6062,28 +6070,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>3.92</v>
+        <v>5.3</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>0.0316</v>
+        <v>0.0251</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>656600</v>
+        <v>1087700</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
       <c r="H125" t="n">
-        <v>58.91</v>
+        <v>52.42</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6091,10 +6099,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>3.812</v>
+        <v>5.234</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>3.496</v>
+        <v>5.287</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6107,28 +6115,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.675</v>
+        <v>2.6</v>
       </c>
       <c r="E126" s="15" t="n">
-        <v>0.0305</v>
+        <v>0.0039</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>627700</v>
+        <v>1073900</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="H126" t="n">
-        <v>72.33</v>
+        <v>41.31</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6136,10 +6144,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.603</v>
+        <v>2.655</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.513</v>
+        <v>2.823</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6152,39 +6160,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0.0046</v>
+        <v>0.285</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>625800</v>
+        <v>1065200</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.53</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>13.097</v>
+        <v>0.294</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>13.67</v>
+        <v>0.31</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6197,28 +6205,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WCEHB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0.0072</v>
+        <v>1.45</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>616700</v>
+        <v>1060700</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.14</v>
+        <v>0.21</v>
       </c>
       <c r="H128" t="n">
-        <v>48.74</v>
+        <v>43.49</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6226,10 +6234,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.703</v>
+        <v>1.466</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.694</v>
+        <v>1.47</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6242,28 +6250,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0.0091</v>
+        <v>1.19</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>615900</v>
+        <v>1034600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="H129" t="n">
-        <v>28.2</v>
+        <v>28.73</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6271,10 +6279,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.608</v>
+        <v>1.332</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.651</v>
+        <v>1.317</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6296,19 +6304,19 @@
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="E130" s="15" t="n">
-        <v>0.0158</v>
+        <v>0.0217</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>614200</v>
+        <v>1017800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H130" t="n">
-        <v>58.76</v>
+        <v>60.18</v>
       </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
@@ -6316,10 +6324,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>5.003</v>
+        <v>5.006</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>5.049</v>
+        <v>5.05</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6332,28 +6340,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>0.0131</v>
+        <v>0.0157</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>593000</v>
+        <v>940800</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="H131" t="n">
-        <v>33.31</v>
+        <v>41.78</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6361,10 +6369,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>3.22</v>
+        <v>1.309</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>3.426</v>
+        <v>1.41</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6377,28 +6385,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.825</v>
+        <v>7.66</v>
       </c>
       <c r="E132" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.0013</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>583400</v>
+        <v>935700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H132" t="n">
-        <v>53.06</v>
+        <v>44.28</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6406,10 +6414,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.825</v>
+        <v>7.767</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.751</v>
+        <v>7.751</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6422,28 +6430,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>-0.0071</v>
+        <v>1.86</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>578200</v>
+        <v>914100</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H133" t="n">
-        <v>62.49</v>
+        <v>35.09</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6451,10 +6459,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.37</v>
+        <v>1.926</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.333</v>
+        <v>2.049</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6467,39 +6475,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>3.16</v>
+        <v>2.92</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>-0.0156</v>
+        <v>-0.0068</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>572000</v>
+        <v>857400</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H134" t="n">
-        <v>62.39</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.62</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>2.955</v>
+        <v>2.97</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>2.763</v>
+        <v>3.033</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6512,39 +6520,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.96</v>
+        <v>0.625</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0246</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>570000</v>
+        <v>850700</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.15</v>
+        <v>0.83</v>
       </c>
       <c r="H135" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.84999999999999</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.983</v>
+        <v>0.552</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.035</v>
+        <v>0.533</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6557,39 +6565,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.78</v>
+        <v>3.96</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.0421</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>568000</v>
+        <v>850600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="H136" t="n">
-        <v>73.34999999999999</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.43</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.726</v>
+        <v>3.816</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.714</v>
+        <v>3.497</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6602,28 +6610,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>7.15</v>
+        <v>2.48</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>-0.0028</v>
+        <v>-0.0159</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>561400</v>
+        <v>839400</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H137" t="n">
-        <v>29.28</v>
+        <v>27.1</v>
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
@@ -6631,10 +6639,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>7.52</v>
+        <v>2.616</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>7.779</v>
+        <v>2.755</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6647,28 +6655,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>0.0013</v>
+        <v>0.545</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>553600</v>
+        <v>825300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="H138" t="n">
-        <v>44.28</v>
+        <v>37.54</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6676,10 +6684,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>7.767</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>7.751</v>
+        <v>0.588</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6692,39 +6700,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>-0.0068</v>
+        <v>13</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>550600</v>
+        <v>793900</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H139" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.6</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>2.97</v>
+        <v>13.096</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>3.033</v>
+        <v>13.669</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6737,28 +6745,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KIPREIT</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="E140" s="15" t="n">
-        <v>0.0058</v>
+        <v>0.0229</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>542500</v>
+        <v>781900</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.96</v>
+        <v>0.38</v>
       </c>
       <c r="H140" t="n">
-        <v>56.73</v>
+        <v>71.69</v>
       </c>
       <c r="I140" s="16" t="inlineStr">
         <is>
@@ -6766,10 +6774,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.854</v>
+        <v>0.603</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.849</v>
+        <v>0.513</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6782,28 +6790,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>-0.0049</v>
+        <v>0.555</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>525400</v>
+        <v>777400</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H141" t="n">
-        <v>42.72</v>
+        <v>28.2</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6811,10 +6819,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.054</v>
+        <v>0.608</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>2.092</v>
+        <v>0.651</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6827,28 +6835,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="E142" s="15" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0163</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>514500</v>
+        <v>751700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="H142" t="n">
-        <v>33.7</v>
+        <v>34.55</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6856,16 +6864,1231 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.578</v>
+        <v>3.221</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.585</v>
+        <v>3.426</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>743100</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H143" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>7.525</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>732700</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H144" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>720900</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H145" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>716600</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H146" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.004699999999999999</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>706600</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H147" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>2.114</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>693200</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H148" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>2.959</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>2.764</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>674100</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H149" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>1.369</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E150" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>670700</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H150" t="n">
+        <v>60.45</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H151" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>8.685</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>8.624000000000001</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>639900</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H152" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>634600</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H153" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>WCEHB</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>622200</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H154" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>614300</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H155" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>2.054</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>2.092</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>604900</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H156" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>4.426</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>597400</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H157" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>595100</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>583600</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H159" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>583500</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H160" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>573800</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H161" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>KEEMING</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>566000</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H162" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5280</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>KIPREIT</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>554800</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H163" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>552300</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H164" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>6.223</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>527100</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H165" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>7.779</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>523700</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H166" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>522800</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H167" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>4.719</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>4.613</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>508300</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H168" t="n">
+        <v>74.79000000000001</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>8.579000000000001</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>8.231</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>503600</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>4.575</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>4.905</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M142"/>
+  <autoFilter ref="A1:M169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
+++ b/docs/downloads/2026-10-05/bursa-report-2026-10-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-05" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-05'!$A$1:$M$292</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M293"/>
+  <dimension ref="A1:M292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，但RSI达69.61接近超买区，现价0.66高于50日均线0.604约9.3%，短线偏热。</t>
+          <t>SAR转多，但RSI 69.61已接近超买区，现价高于50日均线约9.3%，短线偏热。</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，但RSI达71.55已入超买区，现价高于50日均线约8.2%，短线偏热，信号可靠性需谨慎看待。</t>
+          <t>现价0.835高于50日均线0.772，SAR转多信号获均线支撑；但RSI达71.55，已进入超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，但RSI达76.33，处超买区；现价1.12远高于50日均线0.852，乖离偏大，信号可靠性受限。</t>
+          <t>SAR转多信号，但RSI达76.33，处超买区；现价1.12远高于50日均线0.852，乖离偏大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，但RSI达80.11，处超买区；现价1.17远高于50日均线0.885，偏离较大，信号可靠性受限。</t>
+          <t>SAR转多，但RSI达80.11，处超买区；现价1.17远高于50日均线0.885，偏离较大，信号可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价RM 0.42略高于50日均线RM 0.416，RSI 56.04处中性偏上区间，未超买，SAR转多信号技术面尚属合理。</t>
+          <t>现价0.42略高于50日均线0.416，RSI 56处中性偏多区间，未超买，SAR转多信号技术面尚属合理。</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>现价1.38高于50日均线1.169，SAR转多信号获均线支撑；RSI 62.88偏强但未超买，信号可靠性中等偏上。</t>
+          <t>现价RM1.38高于50日均线RM1.169，SAR转多信号获均线支撑；RSI 62.88偏强但未超买，信号可靠性中等偏上。</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，现价0.435高于50日均线0.334约30%，RSI 65.21接近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.435高于50日均线0.334，SAR转多信号获均线支撑；RSI 65.21接近超买区，动能偏强但上行空间受限。</t>
         </is>
       </c>
     </row>
@@ -12087,39 +12087,39 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D258" s="9" t="n">
-        <v>0.225</v>
+        <v>0.245</v>
       </c>
       <c r="E258" s="10" t="n">
-        <v>-0.0217</v>
+        <v>-0.0392</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>1026300</v>
+        <v>1029500</v>
       </c>
       <c r="G258" s="12" t="n">
-        <v>6.85</v>
+        <v>0.45</v>
       </c>
       <c r="H258" t="n">
-        <v>50.57</v>
-      </c>
-      <c r="I258" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.29</v>
+      </c>
+      <c r="I258" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J258" s="9" t="n">
-        <v>0.225</v>
+        <v>0.259</v>
       </c>
       <c r="K258" s="9" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="L258" t="inlineStr"/>
       <c r="M258" s="14" t="inlineStr"/>
@@ -12132,39 +12132,39 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D259" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E259" s="17" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E259" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>1025600</v>
+        <v>1026300</v>
       </c>
       <c r="G259" s="12" t="n">
-        <v>0.44</v>
+        <v>6.85</v>
       </c>
       <c r="H259" t="n">
-        <v>53.26</v>
-      </c>
-      <c r="I259" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.57</v>
+      </c>
+      <c r="I259" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J259" s="9" t="n">
-        <v>0.463</v>
+        <v>0.225</v>
       </c>
       <c r="K259" s="9" t="n">
-        <v>0.461</v>
+        <v>0.225</v>
       </c>
       <c r="L259" t="inlineStr"/>
       <c r="M259" s="14" t="inlineStr"/>
@@ -13617,28 +13617,28 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>UMSINT</t>
         </is>
       </c>
       <c r="D292" s="9" t="n">
-        <v>0.665</v>
+        <v>9.4</v>
       </c>
       <c r="E292" s="15" t="n">
-        <v>0.0153</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>531400</v>
+        <v>519400</v>
       </c>
       <c r="G292" s="12" t="n">
-        <v>0.97</v>
+        <v>1.62</v>
       </c>
       <c r="H292" t="n">
-        <v>53.35</v>
+        <v>74.92</v>
       </c>
       <c r="I292" s="16" t="inlineStr">
         <is>
@@ -13646,61 +13646,16 @@
         </is>
       </c>
       <c r="J292" s="9" t="n">
-        <v>0.658</v>
+        <v>8.58</v>
       </c>
       <c r="K292" s="9" t="n">
-        <v>0.649</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="L292" t="inlineStr"/>
       <c r="M292" s="14" t="inlineStr"/>
     </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>5340</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>UMSINT</t>
-        </is>
-      </c>
-      <c r="D293" s="9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E293" s="15" t="n">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="F293" s="11" t="n">
-        <v>519400</v>
-      </c>
-      <c r="G293" s="12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H293" t="n">
-        <v>74.92</v>
-      </c>
-      <c r="I293" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J293" s="9" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="K293" s="9" t="n">
-        <v>8.231999999999999</v>
-      </c>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M293"/>
+  <autoFilter ref="A1:M292"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>